--- a/backend/exports/yandaojie/deliverables/packets_validity/packet_英语_T3.xlsx
+++ b/backend/exports/yandaojie/deliverables/packets_validity/packet_英语_T3.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编码手册" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标注表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分SOP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对齐练习" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标注表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +48,11 @@
     <font>
       <name val="Arial"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -132,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,25 +182,31 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -856,6 +869,619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>评分流程 SOP（标注前必读）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>1. 读手册</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>先读「编码手册」sheet，重点记 ②辩护深度 的 5 档定义与 4 条判别规则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2. 对齐练习(norming)</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>三位老师各自**独立**标完「对齐练习」sheet 的 8 条 → 与主持人手中的 gold key 逐条对照 → 讨论分歧（重点：对标签错机制 vs 空洞、语言科→难判断）→ 统一理解。对齐后再开始正式标注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>3. 正式标注</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>在「标注表」逐行**独立**标注 ①MC视角 ②辩护深度 ③揭示了什么(引用一句) ④信心。三位老师互不商量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>原则</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>①只看学生说出的答案；②看整段辩护；二者**独立**。只要追问下机制站不住，就**不算“扎实”**（哪怕答案全对）。信息不足 → 难判断 + 低信心。语言科若无可辩护的机制 → 难判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>节奏</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>每条约 2–3 分钟；进入下一条后不回改上一条。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>交回文件；研究者计算评分员信度(κ)。若某维度 κ&lt;0.6，回到 norming 再对齐一轮后重标该批。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>课题</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>本课学习目标</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>学生反思（输入）</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>完整辩护对话（AI追问 → 学生作答，逐轮）</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>①MC视角
+(只看答案/结论)</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>②辩护深度
+(看完整辩护)</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>③辩护揭示了什么(引用一句)</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>④信心(1–5)</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>评分老师</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>数6</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对前后的数同时乘或除以一个相同的数，图形形状不变。」</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你在方格纸上放大图形时，具体是怎么改变数对的？请用小猫乐乐的一个点举例说明变化前后的数对。
+    学生：「(0,2)同时乘2得（0，4）」
+R2 AI：你把(0,2)乘2变成了(0,4)，那么小猫的其他点应该怎么变化？请解释原因。
+    学生：「前后同时乘2，因为都乘2，图形不变」
+R3 AI：你刚才说“图形不变”，但放大后的图形应该变大了呀，你觉得这里的“图形不变”是什么意思？
+    学生：「（空）」
+R4 AI：你刚才提到“图形不变”，但放大后的图形大小改变了，为什么还说图形不变呢？请解释一下你的想法。
+    学生：「是图形形状不变」</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="21" t="n"/>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>数2</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对里的两个数字同时乘一个不为零的数字与原来图形相向」；疑问=「无」</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你说“数对里的两个数字同时乘一个不为零的数字与原来图形相向”，这里的“相向”是指图形形状不变吗？如果我们将小猫乐乐每个点的数对都乘2，画出新图形后，新图形和原图形相比到底发生了什么变化？为什么会这样？
+    学生：「是原图形的每条线段按比例放大到原来的二分之一」
+R2 AI：你刚才说将每个点的数对乘2后，新图形的每条线段按比例放大到原来的二分之一，为什么是二分之一而不是2倍呢？请解释你的想法。
+    学生：「说错了不好意思，是两倍」
+R3 AI：你刚才说乘2后图形变成原来的两倍，那如果想将小猫乐乐缩小到原来的一半，你会如何改变数对？为什么这样做？
+    学生：「将数对的两个数字同时乘二分之一，因为这样会按比例缩小，不影响形状」
+R4 AI：你在反思中提到“乘一个不为零的数字”，如果乘0，会画出什么图形？请解释你的想法。
+    学生：「任何数字乘0都等于0，将两个数字都乘0就没有图形了」
+R4 AI：你刚才说乘0后就没有图形了，但如果所有点都在(0,0)，在方格纸上我们能画出什么？请解释你的想法。
+    学生：「任何数字乘0都等于0，将两个数字都乘0就没有图形了」</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="21" t="n"/>
+      <c r="K3" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>数1</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对的横轴，纵轴和数对的表示方法」</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你已经知道数对可以表示方格纸上的点，如果要把小猫乐乐的图形放大到原来的2倍，你认为每个点的数对应该怎样变化？请解释你的想法。
+    学生：「如果是(2,8),变成（4，16）」
+R2 AI：你提到将数对的两个数都乘以2，这样新的点位置有什么变化？画出的新图形大小和形状会怎样？请解释你的理由。
+    学生：「会向上向右2格，」</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="22" t="n"/>
+      <c r="J4" s="21" t="n"/>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>数29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「横轴与纵轴，在数对中横轴与纵轴同时乘或除以一个相同的数（0除外）得到的图形与图形最像。」</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你说横轴与纵轴同时乘或除以一个相同的数得到的图形最像，请解释为什么这样做得到的图形会最像呢？
+    学生：「因为当设前项为x，后项为y,」
+R2 AI：你说“因为当设前项为x，后项为y,”，请把你的想法说完，解释为什么横轴和纵轴同时乘或除以相同的数，图形就会最像？
+    学生：「（空）」
+R3 AI：你上次写到“因为当设前项为x，后项为y,”，请以小猫图形上的一个点为例，说明为什么x和y同时乘相同数后，新图形与原图形形状相似？
+    学生：「（空）」
+R3 AI：你刚才说‘当第一项乘一个数，第二项也乘一个相同的数，前后可以约分，就是x，’，请你用一个具体的点，比如小猫身上的点(3,2)，把这句话说完，解释为什么这样做就能让图形形状不变？
+    学生：「（空）」
+R4 AI：你提到“前后可以约分，就是x”，请用小猫身上的点(3,2)为例，把这句话说完，解释把(3,2)的横纵坐标都乘2后，新点(6,4)与原点相比，为什么图形形状不变？
+    学生：「因为6除以2等于3 ，4除以2等于2，他们都是除以一个相同的数得出（3，2）」</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="21" t="n"/>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>数15</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「如何观察不同数对
+找数对中不同的规律
+根据规律画出图案」</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你提到通过找数对的规律来画出图案，请具体说说，你是怎样从原图数对得到放大的数对的？
+    学生：「观察前后的数找倍数关系」
+R2 AI：你提到“观察前后的数找倍数关系”，请以小猫的一个点为例，具体说说你是怎样用这个倍数关系从原点对得到新点对的？
+    学生：「若前面的数对为（2，3），后面的为（4，6），」
+R3 AI：你举的例子中（4,6）是（2,3）的两倍，那么小猫的其他点是否也都用了相同的两倍关系？请以另一个点为例说明。
+    学生：「有，比如：（3，5）和（6，10）为两倍关系」
+R4 AI：你通过乘以2得到了放大后的数对并画出了新图形，请问画出的放大图与原来的小猫像吗？结合你的画图经验说明理由。
+    学生：「像，因为按照等比例放大或缩小，图形的整体会比较相似。」
+R4 AI：你说等比例放大图形会相似，那么如果要把小猫缩小到原来的一半，数对应该怎么变化？请以（6,10）为例说明。
+    学生：「像，因为按照等比例放大或缩小，图形的整体会比较相似。」</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>数24</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对各点按等比例扩大或缩小才与原图形最像」；疑问=「无」</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你提到“数对各点按等比例扩大或缩小才与原图形最像”，那请结合小猫乐乐的某个点，说说你是怎样用数对进行等比例放大的？
+    学生：「例如a点 它对应的数对是（x，y） 必须是（bx，by）」
+R2 AI：你用“(bx, by)”放大了a点，那么小猫乐乐身上其他点的数对也需要乘以同一个b吗？如果b不一样会发生什么？
+    学生：「（空）」
+R3 AI：你在反思中说‘数对各点按等比例扩大或缩小才与原图形最像’，那么如果小猫乐乐的不同点乘以不同的b，图形会变成什么样？请结合你的反思解释一下。
+    学生：「因为第一个数是都乘2 而第二个不是这样」
+R3 AI：你用数对举例说明一下，比如原图有两点A(1,1)和B(1,3)，如果A放大为(2,2)而B放大为(2,5)，它们的边长比例与原图相比怎么不同了？
+    学生：「因为第一个数是都乘2 而第二个不是这样」
+R3 AI：你说第一个数都乘2，第二个不是这样，那么B点的纵坐标从3变成5是乘以了几？这导致竖直边AB的长度比原来扩大了多少倍？
+    学生：「因为第一个数是都乘2 而第二个不是这样」</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>科2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「我学到了物质的变化有化学变化也有物理变化，化学变化是产生了新的物质，物理变化是没有产生新物质」</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你提到化学变化产生新物质，物理变化没有，那么你能从厨房里找出一个物理变化和一个化学变化的例子，并用这个标准解释为什么这样分类吗？
+    学生：「比如化学变化有鸡蛋从神的变化成sh」
+R2 AI：你提到了鸡蛋从“神”的变化成“sh”，老师不太确定你想说的是不是“生的变成熟的”？请你完整地说一说鸡蛋煮熟的过程是否符合产生新物质的标准，为什么？
+    学生：「（空）」
+R3 AI：你上次说鸡蛋从生的变成熟的，请你现在完整地解释一下：鸡蛋煮熟后有没有产生新物质？为什么？
+    学生：「产生了因为他产生了气味」
+R4 AI：你说鸡蛋煮熟产生了气味，所以觉得产生了新物质。但气味也可能是鸡蛋里原来的物质受热挥发出来的。你怎么判断这个气味是煮的过程里新生成的物质，而不是原来就有的呢？
+    学生：「（空）」
+R5 AI：你还没回答气味是原有的还是新生成的，那换个角度想一想：除了气味，鸡蛋煮熟前后还有什么明显的变化？这些变化能不能说明产生了新物质？
+    学生：「比如它产生了发热和蛋白从变白」</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>英20</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「学到了做暑假计划」</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你的暑假计划是什么？请用英语回答。
+    学生：「shanghai」
+R1 AI：你说的“Play”，具体要去哪里玩呢？请用英语回答。
+    学生：「shanghai」
+R2 AI：你在上海具体要做什么？请用英语回答。
+    学生：「play」
+R3 AI：你一直说“play”，能详细说说你在上海打算玩什么娱乐项目或运动吗？请用英语回答。
+    学生：「iat」
+R4 AI：你怎么去上海？请用英语回答。
+    学生：「by plane」</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="G2:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"已掌握,部分,未掌握"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"扎实,对标签错机制,空洞或猜对,完全不懂,难判断"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -874,98 +1500,98 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>学生</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>课题</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>本课学习目标</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>学生反思（输入）</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>完整辩护对话（AI追问 → 学生作答，逐轮）</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>①MC视角
 (只看答案/结论)</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>②辩护深度
 (看完整辩护)</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>③辩护揭示了什么(引用一句)</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>④信心(1–5)</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>评分老师</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>英27</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学会了如何用英文描述我的暑假」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能用英语介绍一下你今年暑假打算做什么吗？请用英语回答。
     学生：「I am going to Chengdu and do homework.」
@@ -979,46 +1605,46 @@
     学生：「Hot pot.」</t>
         </is>
       </c>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L2" s="22" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="21" t="n"/>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="n"/>
     </row>
     <row r="3" ht="150" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>英3</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「英语」</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语说说你今年暑假的计划，比如你想去哪里、怎么去。
     学生：「Go  to san ya by  palm」
@@ -1032,46 +1658,46 @@
     学生：「Swam.」</t>
         </is>
       </c>
-      <c r="G3" s="19" t="n"/>
-      <c r="H3" s="19" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="19" t="n"/>
-      <c r="K3" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L3" s="22" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="21" t="n"/>
+      <c r="K3" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="n"/>
     </row>
     <row r="4" ht="150" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>英9</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学习到了交通工具地描述」</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你计划在暑假乘坐什么交通工具去旅行？请用英语解释为什么选择它。
     学生：「no」
@@ -1085,46 +1711,46 @@
     学生：「it's cheap」</t>
         </is>
       </c>
-      <c r="G4" s="19" t="n"/>
-      <c r="H4" s="19" t="n"/>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="19" t="n"/>
-      <c r="K4" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L4" s="22" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="22" t="n"/>
+      <c r="J4" s="21" t="n"/>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="n"/>
     </row>
     <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>英26</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「没有」</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你以前学过关于旅行或者假期的英语单词或句子吗？请试着说出几个你还记得的。
     学生：「没有」
@@ -1138,46 +1764,46 @@
     学生：「no」</t>
         </is>
       </c>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L5" s="22" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="21" t="n"/>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="n"/>
     </row>
     <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>英13</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「怎么表达暑假」</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语回答：What did you do last summer vacation?
     学生：「I   did  homewor」
@@ -1191,46 +1817,46 @@
     学生：「is so diffcult」</t>
         </is>
       </c>
-      <c r="G6" s="19" t="n"/>
-      <c r="H6" s="19" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="19" t="n"/>
-      <c r="K6" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L6" s="22" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="n"/>
     </row>
     <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>英24</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「如何制定出游计划」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你学会了制定出游计划，那你能用英语描述一下你最喜欢的暑假旅行计划吗？
     学生：「I am going to Sanya」
@@ -1244,46 +1870,46 @@
     学生：「By plane」</t>
         </is>
       </c>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="19" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="n"/>
     </row>
     <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>英16</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「制定假期计划」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你暑假打算怎样度过？请用英语回答。
     学生：「nice」
@@ -1297,46 +1923,46 @@
     学生：「eat ice」</t>
         </is>
       </c>
-      <c r="G8" s="19" t="n"/>
-      <c r="H8" s="19" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="19" t="n"/>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="n"/>
     </row>
     <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>英21</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学习到了如何描述交通工具，如何描述我的暑假」；疑问=「no」</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你刚才提到学了描述交通工具和暑假，请用英语说说你上一个暑假怎么去旅行的？
     学生：「going to chong qing by car.」
@@ -1350,46 +1976,46 @@
     学生：「by car」</t>
         </is>
       </c>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="19" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="19" t="n"/>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L9" s="22" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="n"/>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>英4</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「单词」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>R1 AI：What is your favorite transportation for summer vacation and why? Please answer in English.
     学生：「car is fast」
@@ -1403,46 +2029,46 @@
     学生：「becaus we need oil」</t>
         </is>
       </c>
-      <c r="G10" s="19" t="n"/>
-      <c r="H10" s="19" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="19" t="n"/>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="n"/>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>英28</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「交通工具的英文，将来时态」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你暑假打算怎么去旅行？为什么选择这种方式？
     学生：「by car  it is cheap」
@@ -1456,46 +2082,46 @@
     学生：「earth」</t>
         </is>
       </c>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L11" s="22" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="n"/>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>英23</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学会了怎么规划假期」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你计划今年暑假去哪里旅行？请用英语告诉我们你打算做什么。
     学生：「I going to Dhengdu.」
@@ -1509,46 +2135,46 @@
     学生：「go to shop.」</t>
         </is>
       </c>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L12" s="22" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="n"/>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>英34</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「怎么表达自己的暑假」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你学会了表达自己的暑假，请用英语说说你今年的暑假计划吧。
     学生：「play」
@@ -1562,46 +2188,46 @@
     学生：「going to'」</t>
         </is>
       </c>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L13" s="22" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="n"/>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>英30</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学到了如何用英语表达暑假计划」</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>R1 AI：既然你学到了如何用英语表达暑假计划，请用英语告诉我你的暑假旅行计划，包括你要去哪里、怎么去和做什么。
     学生：「I am going to sanya with my mom,and I also eat seafood.」
@@ -1615,46 +2241,46 @@
     学生：「I am going to sanya.I going to sanya by car.I can eat seafood on there.」</t>
         </is>
       </c>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="19" t="n"/>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="n"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>英19</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「英语」</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语告诉我你的暑假计划？
     学生：「I will play video game.」
@@ -1668,46 +2294,46 @@
     学生：「I will go to the Zi Gong eat delicious food,like pizza.」</t>
         </is>
       </c>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="n"/>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>英15</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「怎么表达我的暑假出行方式」；疑问=「更加精确的表达方式」</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>R1 AI：根据你的反思，你想更精确表达暑假出行方式。你能用英语详细说说你今年暑假打算怎么去旅行吗？请用英语回答。
     学生：「i by plane」
@@ -1721,46 +2347,46 @@
     学生：「I also want eat seafood」</t>
         </is>
       </c>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="19" t="n"/>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L16" s="22" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="21" t="n"/>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>英25</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「单词」；疑问=「其它单词」</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能说出几个有关暑假活动的英语单词或短语，并试着用它们造一个句子吗？
     学生：「go home」
@@ -1774,46 +2400,46 @@
     学生：「My friends.」</t>
         </is>
       </c>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="19" t="n"/>
-      <c r="K17" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="21" t="n"/>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>英12</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学到了一片新的文章，还有制定暑期计划，还有出行方式」</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你去年暑假乘坐什么交通工具去旅行的？请用英语回答。
     学生：「By plane.」
@@ -1827,46 +2453,46 @@
     学生：「I swam a lot.」</t>
         </is>
       </c>
-      <c r="G18" s="19" t="n"/>
-      <c r="H18" s="19" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="19" t="n"/>
-      <c r="K18" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L18" s="22" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="21" t="n"/>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L18" s="24" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>英7</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「没有」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你打算这个暑假去哪里旅行？请用英语回答。
     学生：「没有去认和地方」
@@ -1880,46 +2506,46 @@
     学生：「不知道你在说什么」</t>
         </is>
       </c>
-      <c r="G19" s="19" t="n"/>
-      <c r="H19" s="19" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="19" t="n"/>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="21" t="n"/>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>英32</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我会表达暑假」</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语说说你今年暑假打算做什么，请至少提到一种交通方式和计划去的一个地方。
     学生：「l am」
@@ -1933,46 +2559,46 @@
     学生：「I am going to Chengdu by trian withmy family,I am going to eat tasty food there.」</t>
         </is>
       </c>
-      <c r="G20" s="19" t="n"/>
-      <c r="H20" s="19" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="19" t="n"/>
-      <c r="K20" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="21" t="n"/>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="n"/>
     </row>
     <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>英14</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「订制暑假计划」</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语描述你的暑假旅行计划，包括目的地和交通方式，并解释为什么选择该方式。
     学生：「chengdu。By car.」
@@ -1986,46 +2612,46 @@
     学生：「Hot pot and at Wanxiangcheng.」</t>
         </is>
       </c>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L21" s="22" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="n"/>
     </row>
     <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>英11</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我」</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>R1 AI：暑假快到了，如果你能去一个地方旅行，请用英语说说你打算怎么去，以及为什么选择这种交通方式。
     学生：「wfiphd」
@@ -2039,46 +2665,46 @@
     学生：「UKAMW」</t>
         </is>
       </c>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="19" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="19" t="n"/>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L22" s="22" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="n"/>
     </row>
     <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>英8</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「将来时」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语描述你今年暑假的旅行计划，至少说出两个完整的句子。
     学生：「I  am  going」
@@ -2092,46 +2718,46 @@
     学生：「by plane」</t>
         </is>
       </c>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L23" s="24" t="n"/>
     </row>
     <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>英10</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学到了一般将来时写作」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到学到了一般将来时写作，请用英语说说你今年暑假打算去哪里、做什么，至少用两个句子。
     学生：「I am going to Sanya.I am going  to」
@@ -2145,46 +2771,46 @@
     学生：「run,Iam going to run.」</t>
         </is>
       </c>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="19" t="n"/>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L24" s="24" t="n"/>
     </row>
     <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>英5</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学会了如何讲述自己的暑假」</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你说你学会了如何讲述自己的暑假。请用英语详细描述一下你最近的一个暑假经历。
     学生：「My last summervaction I went to Beijing .I ate Beijing duck.」
@@ -2198,46 +2824,46 @@
     学生：「Because it has ears and tail.」</t>
         </is>
       </c>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L25" s="22" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L25" s="24" t="n"/>
     </row>
     <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>英1</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我知道了英语书中的三个女孩她们分别的暑假游玩计划，知道了我该怎末表达暑假旅游」；疑问=「过去式到底有哪些」</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能用英语说说你去年暑假做过的一件事吗？请用英语回答。
     学生：「going  to  HongKong」
@@ -2251,46 +2877,46 @@
     学生：「visit各种项目」</t>
         </is>
       </c>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="I26" s="20" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L26" s="22" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L26" s="24" t="n"/>
     </row>
     <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>英6</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「如何制作暑假计划」</t>
         </is>
       </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到学习如何制作暑假计划，能用英语说说你为自己做的暑假计划吗？
     学生：「I will go to Sanya」
@@ -2304,46 +2930,46 @@
     学生：「Sea ,with my family」</t>
         </is>
       </c>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L27" s="22" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="21" t="n"/>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L27" s="24" t="n"/>
     </row>
     <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>英20</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「学到了做暑假计划」</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你的暑假计划是什么？请用英语回答。
     学生：「shanghai」
@@ -2357,46 +2983,46 @@
     学生：「by plane」</t>
         </is>
       </c>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="19" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L28" s="22" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="21" t="n"/>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L28" s="24" t="n"/>
     </row>
     <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>英2</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「如何表达自己的暑假」</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语说说你的暑假计划吧。
     学生：「I will play game.」
@@ -2410,46 +3036,46 @@
     学生：「I will play chess with my dad inthe park.」</t>
         </is>
       </c>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="20" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L29" s="22" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="n"/>
     </row>
     <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>英35</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「如何规划假期生活」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你如何规划你今年的暑假？请用英语回答。
     学生：「l am going to chengdu」
@@ -2463,46 +3089,46 @@
     学生：「go to chunxi road」</t>
         </is>
       </c>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L30" s="22" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L30" s="24" t="n"/>
     </row>
     <row r="31" ht="150" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>英31</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「如何表达交通工具英文」；疑问=「别的交通工具英文」</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语回答：你通常如何去上学，并解释为什么选择这种方式？
     学生：「car,it is good」
@@ -2516,46 +3142,46 @@
     学生：「Beacuase it can lose weight.」</t>
         </is>
       </c>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L31" s="22" t="n"/>
+      <c r="G31" s="21" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="n"/>
     </row>
     <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>英18</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「做暑假计划」；疑问=「no」</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>R1 AI：What are your plans for the summer vacation? Please answer in English.
     学生：「Going  to sanya」
@@ -2569,46 +3195,46 @@
     学生：「eat many food and swim in the sea.」</t>
         </is>
       </c>
-      <c r="G32" s="19" t="n"/>
-      <c r="H32" s="19" t="n"/>
-      <c r="I32" s="20" t="n"/>
-      <c r="J32" s="19" t="n"/>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L32" s="22" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="21" t="n"/>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L32" s="24" t="n"/>
     </row>
     <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>英29</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「学会表达交通工具以及将来时态」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F33" s="18" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语告诉我，你暑假将怎样去旅行？
     学生：「i go to Sanya by plane」
@@ -2622,46 +3248,46 @@
     学生：「6 days」</t>
         </is>
       </c>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="20" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L33" s="22" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L33" s="24" t="n"/>
     </row>
     <row r="34" ht="150" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>英22</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「怎么写暑假计划」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语说说你的暑假计划。
     学生：「go to Sanya」
@@ -2675,46 +3301,46 @@
     学生：「I will play game」</t>
         </is>
       </c>
-      <c r="G34" s="19" t="n"/>
-      <c r="H34" s="19" t="n"/>
-      <c r="I34" s="20" t="n"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L34" s="22" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="21" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="21" t="n"/>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L34" s="24" t="n"/>
     </row>
     <row r="35" ht="150" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>英17</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学会了如何用英语表达出行」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>R1 AI：暑假快到了，请用英语说说你的出行计划。（请用英语回答）
     学生：「I am going to Aomeng」
@@ -2728,46 +3354,46 @@
     学生：「it's tall and beautiful.」</t>
         </is>
       </c>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="20" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L35" s="22" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L35" s="24" t="n"/>
     </row>
     <row r="36" ht="150" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>英33</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>Unit 6 Summer Vacation</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
-2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
-3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「如何制定计划」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请用英语告诉我，你今年暑假打算去哪里旅行？为什么选择那里？
     学生：「I  am  going   to   the  USA」
@@ -2781,16 +3407,16 @@
     学生：「JIU   JIN   SHAN」</t>
         </is>
       </c>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="20" t="n"/>
-      <c r="J36" s="19" t="n"/>
-      <c r="K36" s="21" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="L36" s="22" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="21" t="n"/>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="L36" s="24" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
